--- a/outputs/language_summary.xlsx
+++ b/outputs/language_summary.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>language_update</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -440,75 +440,153 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53374</v>
+        <v>21006</v>
       </c>
       <c r="C2" t="n">
-        <v>44.48</v>
+        <v>99.76727618142959</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24297</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>20.25</v>
+        <v>0.09973877938731891</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23501</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>19.58</v>
+        <v>0.03324625979577298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>es</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18792</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>15.66</v>
+        <v>0.02374732842555213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02</v>
+        <v>0.0189978627404417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>de</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01</v>
+        <v>0.0189978627404417</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01424839705533128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sv</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.004749465685110425</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004749465685110425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004749465685110425</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.004749465685110425</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.004749465685110425</v>
       </c>
     </row>
   </sheetData>
